--- a/approval_forms/033_museum_artifact_requisition_form--approval_forms.xlsx
+++ b/approval_forms/033_museum_artifact_requisition_form--approval_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'a'}</t>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'b'}</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'c'}</t>
+          <t>c</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'curator'}</t>
+          <t>curator</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'curator'}</t>
+          <t>curator</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'curator'}</t>
+          <t>curator</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'curator'}</t>
+          <t>curator</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'curator'}</t>
+          <t>curator</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'curator'}</t>
+          <t>curator</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
